--- a/files/plan/N100002464.xlsx
+++ b/files/plan/N100002464.xlsx
@@ -509,7 +509,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: 충남 고등학교 교육과정 편제표 입력 시스템 저장본(2026-10-14 12:12) · 단위: 학점(창체는 시간)</t>
+          <t>출처: 충남 고등학교 교육과정 편제표 입력 시스템 저장본(2026-10-30 09:38) · 단위: 학점(창체는 시간)</t>
         </is>
       </c>
     </row>
